--- a/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
+++ b/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
@@ -28,13 +28,13 @@
     <t>Fecha de realización:</t>
   </si>
   <si>
-    <t>11/02/2025</t>
+    <t>17/02/2025</t>
   </si>
   <si>
     <t>No. de reporte:</t>
   </si>
   <si>
-    <t>PM11022025</t>
+    <t>PM17022025</t>
   </si>
   <si>
     <t>Programado</t>
@@ -61,19 +61,19 @@
     <t>Puesto:</t>
   </si>
   <si>
-    <t>soporte 1</t>
+    <t>SOPORTE 1</t>
   </si>
   <si>
     <t>No. de serie:</t>
   </si>
   <si>
-    <t>22526DDDD</t>
+    <t>ADFASF</t>
   </si>
   <si>
     <t>Capacidad de disco:</t>
   </si>
   <si>
-    <t>1111GB</t>
+    <t>222GB</t>
   </si>
   <si>
     <t>No. de inventario:</t>
@@ -100,13 +100,13 @@
     <t>Eliminación de cookies</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>Exterior teclado y ratón</t>
   </si>
   <si>
     <t>Eliminación de temporales</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Interior / Exterior gabinete</t>
@@ -1324,7 +1324,7 @@
       <c r="J29" s="9"/>
       <c r="K29" s="13"/>
       <c r="L29" s="46" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="M29" s="61"/>
     </row>
@@ -1342,7 +1342,7 @@
     <row r="31" spans="1:14" customHeight="1" ht="13.5">
       <c r="A31" s="9"/>
       <c r="B31" s="53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C31" s="54"/>
       <c r="D31" s="9"/>
@@ -1351,14 +1351,14 @@
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="54" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H31" s="54"/>
       <c r="I31" s="54"/>
       <c r="J31" s="9"/>
       <c r="K31" s="13"/>
       <c r="L31" s="46" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="M31" s="62"/>
     </row>
@@ -1381,7 +1381,7 @@
       <c r="C33" s="54"/>
       <c r="D33" s="9"/>
       <c r="E33" s="46" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="54" t="s">
@@ -1444,7 +1444,7 @@
       <c r="C37" s="54"/>
       <c r="D37" s="9"/>
       <c r="E37" s="46" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F37" s="18"/>
       <c r="G37" s="54" t="s">
@@ -1522,7 +1522,7 @@
         <v>39</v>
       </c>
       <c r="F43" s="47" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H43" s="33"/>
       <c r="I43" s="33"/>
@@ -1594,7 +1594,7 @@
         <v>43</v>
       </c>
       <c r="F51" s="47" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H51" s="33"/>
       <c r="I51" s="33"/>
@@ -1721,7 +1721,7 @@
         <v>49</v>
       </c>
       <c r="F63" s="47" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H63" s="33"/>
       <c r="I63" s="33"/>
@@ -1740,7 +1740,7 @@
         <v>50</v>
       </c>
       <c r="F65" s="47" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H65" s="33"/>
       <c r="I65" s="33"/>
@@ -1759,7 +1759,7 @@
         <v>51</v>
       </c>
       <c r="F67" s="47" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H67" s="33"/>
       <c r="I67" s="33"/>

--- a/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
+++ b/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
   <si>
     <t>Automóviles y Camiones Rivera, S.A. de C.V.</t>
   </si>
@@ -28,13 +28,13 @@
     <t>Fecha de realización:</t>
   </si>
   <si>
-    <t>17/02/2025</t>
+    <t>01/02/2025</t>
   </si>
   <si>
     <t>No. de reporte:</t>
   </si>
   <si>
-    <t>PM17022025</t>
+    <t>PM01022025</t>
   </si>
   <si>
     <t>Programado</t>
@@ -61,19 +61,19 @@
     <t>Puesto:</t>
   </si>
   <si>
-    <t>SOPORTE 1</t>
+    <t>Auliira Contable</t>
   </si>
   <si>
     <t>No. de serie:</t>
   </si>
   <si>
-    <t>ADFASF</t>
+    <t>22526DDDD</t>
   </si>
   <si>
     <t>Capacidad de disco:</t>
   </si>
   <si>
-    <t>222GB</t>
+    <t>13GB</t>
   </si>
   <si>
     <t>No. de inventario:</t>
@@ -82,6 +82,9 @@
     <t>Capacidad de memoria:</t>
   </si>
   <si>
+    <t>22GB</t>
+  </si>
+  <si>
     <t>Espacio disponible:</t>
   </si>
   <si>
@@ -187,7 +190,7 @@
     <t>Supervisó</t>
   </si>
   <si>
-    <t>José Arturo Moreno Aguilar</t>
+    <t>Mario Javier Romero Mendoza</t>
   </si>
   <si>
     <t>Abel de Jesús Moral Flores</t>
@@ -263,7 +266,7 @@
       <name val="CorpoS"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -273,12 +276,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1F0C7"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -421,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
@@ -516,21 +513,15 @@
     <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="14" fillId="3" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf xfId="0" fontId="1" numFmtId="14" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -545,13 +536,13 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="49" fillId="3" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="49" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="49" fillId="3" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="49" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -569,10 +560,10 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1006,25 +997,25 @@
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
       <c r="F7" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="54" t="s">
+      <c r="H7" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
-      <c r="K7" s="54"/>
-      <c r="L7" s="50" t="s">
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="M7" s="55"/>
+      <c r="M7" s="53"/>
     </row>
     <row r="8" spans="1:14" customHeight="1" ht="7.5">
       <c r="B8" s="11"/>
@@ -1032,19 +1023,19 @@
     </row>
     <row r="9" spans="1:14" customHeight="1" ht="13.5">
       <c r="A9" s="9"/>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="54"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="45" t="s">
         <v>7</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="54" t="s">
+      <c r="H9" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="54"/>
+      <c r="I9" s="52"/>
       <c r="J9" s="45"/>
       <c r="K9" s="13"/>
       <c r="L9" s="9"/>
@@ -1067,22 +1058,22 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="9"/>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="54"/>
+      <c r="C11" s="52"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="55"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="53"/>
     </row>
     <row r="12" spans="1:14" customHeight="1" ht="7.5">
       <c r="A12" s="9"/>
@@ -1130,22 +1121,22 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="9"/>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="49"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="21"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="55"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="53"/>
     </row>
     <row r="16" spans="1:14" customHeight="1" ht="7.5">
       <c r="B16" s="11"/>
@@ -1155,22 +1146,22 @@
       <c r="B17" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="H17" s="49" t="s">
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="H17" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="49"/>
-      <c r="J17" s="56" t="s">
+      <c r="I17" s="47"/>
+      <c r="J17" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="K17" s="56"/>
-      <c r="L17" s="56"/>
-      <c r="M17" s="57"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="55"/>
     </row>
     <row r="18" spans="1:14" customHeight="1" ht="7.5">
       <c r="B18" s="11"/>
@@ -1178,23 +1169,23 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="9"/>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="50" t="s">
+      <c r="C19" s="47"/>
+      <c r="D19" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="H19" s="49" t="s">
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="H19" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="49"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="52"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="50"/>
     </row>
     <row r="20" spans="1:14" customHeight="1" ht="7.5">
       <c r="B20" s="11"/>
@@ -1202,23 +1193,23 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="9"/>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
       <c r="H21" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I21" s="21"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="52"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="50"/>
     </row>
     <row r="22" spans="1:14" customHeight="1" ht="7.5">
       <c r="B22" s="11"/>
@@ -1226,22 +1217,22 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="9"/>
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="54"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="51"/>
-      <c r="M23" s="52"/>
+      <c r="E23" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="49"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="50"/>
     </row>
     <row r="24" spans="1:14" customHeight="1" ht="7.5">
       <c r="A24" s="9"/>
@@ -1281,21 +1272,21 @@
       <c r="M26" s="7"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="B27" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="H27" s="59" t="s">
+      <c r="B27" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
-      <c r="M27" s="60"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="H27" s="57" t="s">
+        <v>25</v>
+      </c>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="58"/>
     </row>
     <row r="28" spans="1:14" customHeight="1" ht="7.5">
       <c r="A28" s="9"/>
@@ -1307,26 +1298,26 @@
     </row>
     <row r="29" spans="1:14" customHeight="1" ht="13.5">
       <c r="A29" s="9"/>
-      <c r="B29" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="54"/>
+      <c r="B29" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="52"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="46" t="s">
+      <c r="E29" s="13" t="s">
         <v>7</v>
       </c>
       <c r="F29" s="9"/>
-      <c r="G29" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
+      <c r="G29" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
       <c r="J29" s="9"/>
       <c r="K29" s="13"/>
-      <c r="L29" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29" s="61"/>
+      <c r="L29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M29" s="59"/>
     </row>
     <row r="30" spans="1:14" customHeight="1" ht="7.5">
       <c r="B30" s="28"/>
@@ -1337,30 +1328,30 @@
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
-      <c r="M30" s="62"/>
+      <c r="M30" s="60"/>
     </row>
     <row r="31" spans="1:14" customHeight="1" ht="13.5">
       <c r="A31" s="9"/>
-      <c r="B31" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="54"/>
+      <c r="B31" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="52"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="46" t="s">
+      <c r="E31" s="13" t="s">
         <v>7</v>
       </c>
       <c r="F31" s="9"/>
-      <c r="G31" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
+      <c r="G31" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
       <c r="J31" s="9"/>
       <c r="K31" s="13"/>
-      <c r="L31" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="M31" s="62"/>
+      <c r="L31" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M31" s="60"/>
     </row>
     <row r="32" spans="1:14" customHeight="1" ht="7.5">
       <c r="B32" s="8"/>
@@ -1375,20 +1366,20 @@
     </row>
     <row r="33" spans="1:14" customHeight="1" ht="13.5">
       <c r="A33" s="9"/>
-      <c r="B33" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="54"/>
+      <c r="B33" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="52"/>
       <c r="D33" s="9"/>
-      <c r="E33" s="46" t="s">
-        <v>27</v>
+      <c r="E33" s="13" t="s">
+        <v>7</v>
       </c>
       <c r="F33" s="9"/>
-      <c r="G33" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
+      <c r="G33" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
       <c r="J33" s="9"/>
       <c r="K33" s="29"/>
       <c r="L33" s="9"/>
@@ -1407,19 +1398,19 @@
     </row>
     <row r="35" spans="1:14" customHeight="1" ht="13.5">
       <c r="A35" s="9"/>
-      <c r="B35" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="54"/>
+      <c r="B35" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="52"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="46" t="s">
+      <c r="E35" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="H35" s="54"/>
-      <c r="I35" s="54"/>
+      <c r="G35" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
       <c r="J35" s="9"/>
       <c r="K35" s="29"/>
       <c r="L35" s="9"/>
@@ -1438,20 +1429,20 @@
     </row>
     <row r="37" spans="1:14" customHeight="1" ht="13.5">
       <c r="A37" s="9"/>
-      <c r="B37" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="54"/>
+      <c r="B37" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="52"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="46" t="s">
-        <v>27</v>
+      <c r="E37" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F37" s="18"/>
-      <c r="G37" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="H37" s="54"/>
-      <c r="I37" s="54"/>
+      <c r="G37" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
       <c r="J37" s="9"/>
       <c r="K37" s="29"/>
       <c r="L37" s="18"/>
@@ -1503,26 +1494,26 @@
     </row>
     <row r="41" spans="1:14">
       <c r="B41" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M41" s="12"/>
     </row>
     <row r="42" spans="1:14">
       <c r="B42" s="11"/>
       <c r="F42" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M42" s="14"/>
     </row>
     <row r="43" spans="1:14" customHeight="1" ht="13.5">
       <c r="B43" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F43" s="47" t="s">
-        <v>27</v>
+        <v>40</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>28</v>
       </c>
       <c r="H43" s="33"/>
       <c r="I43" s="33"/>
@@ -1537,9 +1528,9 @@
     </row>
     <row r="45" spans="1:14" customHeight="1" ht="13.5">
       <c r="B45" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F45" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="F45" s="32" t="s">
         <v>7</v>
       </c>
       <c r="H45" s="33"/>
@@ -1555,9 +1546,9 @@
     </row>
     <row r="47" spans="1:14" customHeight="1" ht="13.5">
       <c r="B47" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F47" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="32" t="s">
         <v>7</v>
       </c>
       <c r="H47" s="33"/>
@@ -1573,9 +1564,9 @@
     </row>
     <row r="49" spans="1:14" customHeight="1" ht="13.5">
       <c r="B49" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F49" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="F49" s="32" t="s">
         <v>7</v>
       </c>
       <c r="H49" s="33"/>
@@ -1591,10 +1582,10 @@
     </row>
     <row r="51" spans="1:14" customHeight="1" ht="13.5">
       <c r="B51" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F51" s="47" t="s">
-        <v>27</v>
+        <v>44</v>
+      </c>
+      <c r="F51" s="32" t="s">
+        <v>7</v>
       </c>
       <c r="H51" s="33"/>
       <c r="I51" s="33"/>
@@ -1643,7 +1634,7 @@
     </row>
     <row r="55" spans="1:14">
       <c r="B55" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F55" s="18"/>
       <c r="H55" s="18"/>
@@ -1652,19 +1643,19 @@
     <row r="56" spans="1:14" customHeight="1" ht="12">
       <c r="B56" s="11"/>
       <c r="F56" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M56" s="14"/>
     </row>
     <row r="57" spans="1:14" customHeight="1" ht="13.5">
       <c r="B57" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F57" s="47" t="s">
-        <v>7</v>
+        <v>47</v>
+      </c>
+      <c r="F57" s="32" t="s">
+        <v>28</v>
       </c>
       <c r="H57" s="33"/>
       <c r="I57" s="33"/>
@@ -1680,9 +1671,9 @@
     </row>
     <row r="59" spans="1:14" customHeight="1" ht="13.5">
       <c r="B59" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F59" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="F59" s="32" t="s">
         <v>7</v>
       </c>
       <c r="H59" s="33"/>
@@ -1699,9 +1690,9 @@
     </row>
     <row r="61" spans="1:14" customHeight="1" ht="13.5">
       <c r="B61" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F61" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="F61" s="32" t="s">
         <v>7</v>
       </c>
       <c r="H61" s="33"/>
@@ -1718,10 +1709,10 @@
     </row>
     <row r="63" spans="1:14" customHeight="1" ht="13.5">
       <c r="B63" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F63" s="47" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="F63" s="32" t="s">
+        <v>7</v>
       </c>
       <c r="H63" s="33"/>
       <c r="I63" s="33"/>
@@ -1737,10 +1728,10 @@
     </row>
     <row r="65" spans="1:14" customHeight="1" ht="13.5">
       <c r="B65" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F65" s="47" t="s">
-        <v>27</v>
+        <v>51</v>
+      </c>
+      <c r="F65" s="32" t="s">
+        <v>7</v>
       </c>
       <c r="H65" s="33"/>
       <c r="I65" s="33"/>
@@ -1756,10 +1747,10 @@
     </row>
     <row r="67" spans="1:14" customHeight="1" ht="13.5">
       <c r="B67" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F67" s="47" t="s">
-        <v>27</v>
+        <v>52</v>
+      </c>
+      <c r="F67" s="32" t="s">
+        <v>28</v>
       </c>
       <c r="H67" s="33"/>
       <c r="I67" s="33"/>
@@ -1774,7 +1765,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="B69" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F69" s="33"/>
       <c r="H69" s="33"/>
@@ -1815,27 +1806,27 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="18"/>
-      <c r="B73" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="C73" s="59"/>
+      <c r="B73" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="C73" s="57"/>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
-      <c r="F73" s="59" t="s">
-        <v>54</v>
-      </c>
-      <c r="G73" s="59"/>
-      <c r="H73" s="59"/>
-      <c r="I73" s="59"/>
-      <c r="L73" s="59" t="s">
+      <c r="F73" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="M73" s="60"/>
+      <c r="G73" s="57"/>
+      <c r="H73" s="57"/>
+      <c r="I73" s="57"/>
+      <c r="L73" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="M73" s="58"/>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="18"/>
-      <c r="B74" s="65"/>
-      <c r="C74" s="66"/>
+      <c r="B74" s="63"/>
+      <c r="C74" s="64"/>
       <c r="D74" s="18"/>
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
@@ -1852,22 +1843,22 @@
     </row>
     <row r="76" spans="1:14" customHeight="1" ht="33">
       <c r="A76" s="18"/>
-      <c r="B76" s="63" t="s">
+      <c r="B76" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C76" s="64"/>
+      <c r="C76" s="62"/>
       <c r="D76" s="18"/>
       <c r="E76" s="18"/>
-      <c r="F76" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="G76" s="51"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="51"/>
-      <c r="L76" s="51" t="s">
+      <c r="F76" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="M76" s="52"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
+      <c r="L76" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="M76" s="50"/>
     </row>
     <row r="77" spans="1:14" customHeight="1" ht="8.25">
       <c r="B77" s="34"/>

--- a/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
+++ b/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
   <si>
     <t>Automóviles y Camiones Rivera, S.A. de C.V.</t>
   </si>
@@ -28,13 +28,13 @@
     <t>Fecha de realización:</t>
   </si>
   <si>
-    <t>01/02/2025</t>
+    <t>18/02/2025</t>
   </si>
   <si>
     <t>No. de reporte:</t>
   </si>
   <si>
-    <t>PM01022025</t>
+    <t>PM18022025</t>
   </si>
   <si>
     <t>Programado</t>
@@ -61,7 +61,7 @@
     <t>Puesto:</t>
   </si>
   <si>
-    <t>Auliira Contable</t>
+    <t>Soporte 1</t>
   </si>
   <si>
     <t>No. de serie:</t>
@@ -73,7 +73,7 @@
     <t>Capacidad de disco:</t>
   </si>
   <si>
-    <t>13GB</t>
+    <t>11GB</t>
   </si>
   <si>
     <t>No. de inventario:</t>
@@ -82,9 +82,6 @@
     <t>Capacidad de memoria:</t>
   </si>
   <si>
-    <t>22GB</t>
-  </si>
-  <si>
     <t>Espacio disponible:</t>
   </si>
   <si>
@@ -100,12 +97,12 @@
     <t>Pantalla</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>Eliminación de cookies</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Exterior teclado y ratón</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
   </si>
   <si>
     <t>Supervisó</t>
-  </si>
-  <si>
-    <t>Mario Javier Romero Mendoza</t>
   </si>
   <si>
     <t>Abel de Jesús Moral Flores</t>
@@ -1198,12 +1192,12 @@
       </c>
       <c r="C21" s="47"/>
       <c r="D21" s="48" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E21" s="48"/>
       <c r="F21" s="48"/>
       <c r="H21" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I21" s="21"/>
       <c r="J21" s="49"/>
@@ -1223,7 +1217,7 @@
       <c r="C23" s="52"/>
       <c r="D23" s="9"/>
       <c r="E23" s="49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F23" s="49"/>
       <c r="G23" s="49"/>
@@ -1273,14 +1267,14 @@
     </row>
     <row r="27" spans="1:14">
       <c r="B27" s="56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="57"/>
       <c r="D27" s="57"/>
       <c r="E27" s="57"/>
       <c r="F27" s="57"/>
       <c r="H27" s="57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I27" s="57"/>
       <c r="J27" s="57"/>
@@ -1299,12 +1293,12 @@
     <row r="29" spans="1:14" customHeight="1" ht="13.5">
       <c r="A29" s="9"/>
       <c r="B29" s="51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="52"/>
       <c r="D29" s="9"/>
       <c r="E29" s="13" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="52" t="s">
@@ -1315,7 +1309,7 @@
       <c r="J29" s="9"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M29" s="59"/>
     </row>
@@ -1333,23 +1327,23 @@
     <row r="31" spans="1:14" customHeight="1" ht="13.5">
       <c r="A31" s="9"/>
       <c r="B31" s="51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C31" s="52"/>
       <c r="D31" s="9"/>
       <c r="E31" s="13" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H31" s="52"/>
       <c r="I31" s="52"/>
       <c r="J31" s="9"/>
       <c r="K31" s="13"/>
       <c r="L31" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M31" s="60"/>
     </row>
@@ -1367,16 +1361,16 @@
     <row r="33" spans="1:14" customHeight="1" ht="13.5">
       <c r="A33" s="9"/>
       <c r="B33" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" s="52"/>
       <c r="D33" s="9"/>
       <c r="E33" s="13" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H33" s="52"/>
       <c r="I33" s="52"/>
@@ -1399,15 +1393,15 @@
     <row r="35" spans="1:14" customHeight="1" ht="13.5">
       <c r="A35" s="9"/>
       <c r="B35" s="51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" s="52"/>
       <c r="D35" s="9"/>
       <c r="E35" s="13" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G35" s="52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H35" s="52"/>
       <c r="I35" s="52"/>
@@ -1430,16 +1424,16 @@
     <row r="37" spans="1:14" customHeight="1" ht="13.5">
       <c r="A37" s="9"/>
       <c r="B37" s="51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C37" s="52"/>
       <c r="D37" s="9"/>
       <c r="E37" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F37" s="18"/>
       <c r="G37" s="52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H37" s="52"/>
       <c r="I37" s="52"/>
@@ -1494,26 +1488,26 @@
     </row>
     <row r="41" spans="1:14">
       <c r="B41" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M41" s="12"/>
     </row>
     <row r="42" spans="1:14">
       <c r="B42" s="11"/>
       <c r="F42" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H42" s="18" t="s">
         <v>38</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>39</v>
       </c>
       <c r="M42" s="14"/>
     </row>
     <row r="43" spans="1:14" customHeight="1" ht="13.5">
       <c r="B43" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F43" s="32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H43" s="33"/>
       <c r="I43" s="33"/>
@@ -1528,10 +1522,10 @@
     </row>
     <row r="45" spans="1:14" customHeight="1" ht="13.5">
       <c r="B45" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F45" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H45" s="33"/>
       <c r="I45" s="33"/>
@@ -1546,10 +1540,10 @@
     </row>
     <row r="47" spans="1:14" customHeight="1" ht="13.5">
       <c r="B47" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F47" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H47" s="33"/>
       <c r="I47" s="33"/>
@@ -1564,10 +1558,10 @@
     </row>
     <row r="49" spans="1:14" customHeight="1" ht="13.5">
       <c r="B49" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F49" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H49" s="33"/>
       <c r="I49" s="33"/>
@@ -1582,10 +1576,10 @@
     </row>
     <row r="51" spans="1:14" customHeight="1" ht="13.5">
       <c r="B51" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F51" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H51" s="33"/>
       <c r="I51" s="33"/>
@@ -1634,7 +1628,7 @@
     </row>
     <row r="55" spans="1:14">
       <c r="B55" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F55" s="18"/>
       <c r="H55" s="18"/>
@@ -1643,19 +1637,19 @@
     <row r="56" spans="1:14" customHeight="1" ht="12">
       <c r="B56" s="11"/>
       <c r="F56" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M56" s="14"/>
     </row>
     <row r="57" spans="1:14" customHeight="1" ht="13.5">
       <c r="B57" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H57" s="33"/>
       <c r="I57" s="33"/>
@@ -1671,10 +1665,10 @@
     </row>
     <row r="59" spans="1:14" customHeight="1" ht="13.5">
       <c r="B59" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F59" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H59" s="33"/>
       <c r="I59" s="33"/>
@@ -1690,10 +1684,10 @@
     </row>
     <row r="61" spans="1:14" customHeight="1" ht="13.5">
       <c r="B61" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F61" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H61" s="33"/>
       <c r="I61" s="33"/>
@@ -1709,10 +1703,10 @@
     </row>
     <row r="63" spans="1:14" customHeight="1" ht="13.5">
       <c r="B63" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F63" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H63" s="33"/>
       <c r="I63" s="33"/>
@@ -1728,10 +1722,10 @@
     </row>
     <row r="65" spans="1:14" customHeight="1" ht="13.5">
       <c r="B65" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H65" s="33"/>
       <c r="I65" s="33"/>
@@ -1747,10 +1741,10 @@
     </row>
     <row r="67" spans="1:14" customHeight="1" ht="13.5">
       <c r="B67" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H67" s="33"/>
       <c r="I67" s="33"/>
@@ -1765,7 +1759,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="B69" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F69" s="33"/>
       <c r="H69" s="33"/>
@@ -1807,19 +1801,19 @@
     <row r="73" spans="1:14">
       <c r="A73" s="18"/>
       <c r="B73" s="56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C73" s="57"/>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
       <c r="F73" s="57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G73" s="57"/>
       <c r="H73" s="57"/>
       <c r="I73" s="57"/>
       <c r="L73" s="57" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M73" s="58"/>
     </row>
@@ -1850,13 +1844,13 @@
       <c r="D76" s="18"/>
       <c r="E76" s="18"/>
       <c r="F76" s="49" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="G76" s="49"/>
       <c r="H76" s="49"/>
       <c r="I76" s="49"/>
       <c r="L76" s="49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M76" s="50"/>
     </row>

--- a/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
+++ b/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
@@ -61,19 +61,19 @@
     <t>Puesto:</t>
   </si>
   <si>
-    <t>Soporte 1</t>
+    <t>Asdfas</t>
   </si>
   <si>
     <t>No. de serie:</t>
   </si>
   <si>
-    <t>22526DDDD</t>
+    <t>FASDF</t>
   </si>
   <si>
     <t>Capacidad de disco:</t>
   </si>
   <si>
-    <t>11GB</t>
+    <t>22GB</t>
   </si>
   <si>
     <t>No. de inventario:</t>

--- a/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
+++ b/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
@@ -28,13 +28,13 @@
     <t>Fecha de realización:</t>
   </si>
   <si>
-    <t>18/02/2025</t>
+    <t>19/02/2025</t>
   </si>
   <si>
     <t>No. de reporte:</t>
   </si>
   <si>
-    <t>PM18022025</t>
+    <t>PM19022025</t>
   </si>
   <si>
     <t>Programado</t>
@@ -61,19 +61,19 @@
     <t>Puesto:</t>
   </si>
   <si>
-    <t>Asdfas</t>
+    <t>Soporte 1</t>
   </si>
   <si>
     <t>No. de serie:</t>
   </si>
   <si>
-    <t>FASDF</t>
+    <t>22526DDDD</t>
   </si>
   <si>
     <t>Capacidad de disco:</t>
   </si>
   <si>
-    <t>22GB</t>
+    <t>11GB</t>
   </si>
   <si>
     <t>No. de inventario:</t>

--- a/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
+++ b/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
   <si>
     <t>Automóviles y Camiones Rivera, S.A. de C.V.</t>
   </si>
@@ -28,13 +28,13 @@
     <t>Fecha de realización:</t>
   </si>
   <si>
-    <t>19/02/2025</t>
+    <t>12/03/2025</t>
   </si>
   <si>
     <t>No. de reporte:</t>
   </si>
   <si>
-    <t>PM19022025</t>
+    <t>PM12032025</t>
   </si>
   <si>
     <t>Programado</t>
@@ -61,19 +61,19 @@
     <t>Puesto:</t>
   </si>
   <si>
-    <t>Soporte 1</t>
+    <t>Tt</t>
   </si>
   <si>
     <t>No. de serie:</t>
   </si>
   <si>
-    <t>22526DDDD</t>
+    <t>TT</t>
   </si>
   <si>
     <t>Capacidad de disco:</t>
   </si>
   <si>
-    <t>11GB</t>
+    <t>1GB</t>
   </si>
   <si>
     <t>No. de inventario:</t>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>Pantalla</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Eliminación de cookies</t>
@@ -1298,18 +1295,18 @@
       <c r="C29" s="52"/>
       <c r="D29" s="9"/>
       <c r="E29" s="13" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H29" s="52"/>
       <c r="I29" s="52"/>
       <c r="J29" s="9"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="M29" s="59"/>
     </row>
@@ -1327,23 +1324,23 @@
     <row r="31" spans="1:14" customHeight="1" ht="13.5">
       <c r="A31" s="9"/>
       <c r="B31" s="51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="52"/>
       <c r="D31" s="9"/>
       <c r="E31" s="13" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H31" s="52"/>
       <c r="I31" s="52"/>
       <c r="J31" s="9"/>
       <c r="K31" s="13"/>
       <c r="L31" s="13" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="M31" s="60"/>
     </row>
@@ -1361,16 +1358,16 @@
     <row r="33" spans="1:14" customHeight="1" ht="13.5">
       <c r="A33" s="9"/>
       <c r="B33" s="51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" s="52"/>
       <c r="D33" s="9"/>
       <c r="E33" s="13" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H33" s="52"/>
       <c r="I33" s="52"/>
@@ -1393,15 +1390,15 @@
     <row r="35" spans="1:14" customHeight="1" ht="13.5">
       <c r="A35" s="9"/>
       <c r="B35" s="51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="52"/>
       <c r="D35" s="9"/>
       <c r="E35" s="13" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G35" s="52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H35" s="52"/>
       <c r="I35" s="52"/>
@@ -1424,16 +1421,16 @@
     <row r="37" spans="1:14" customHeight="1" ht="13.5">
       <c r="A37" s="9"/>
       <c r="B37" s="51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="52"/>
       <c r="D37" s="9"/>
       <c r="E37" s="13" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F37" s="18"/>
       <c r="G37" s="52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H37" s="52"/>
       <c r="I37" s="52"/>
@@ -1488,26 +1485,26 @@
     </row>
     <row r="41" spans="1:14">
       <c r="B41" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M41" s="12"/>
     </row>
     <row r="42" spans="1:14">
       <c r="B42" s="11"/>
       <c r="F42" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H42" s="18" t="s">
         <v>37</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>38</v>
       </c>
       <c r="M42" s="14"/>
     </row>
     <row r="43" spans="1:14" customHeight="1" ht="13.5">
       <c r="B43" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F43" s="32" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H43" s="33"/>
       <c r="I43" s="33"/>
@@ -1522,10 +1519,10 @@
     </row>
     <row r="45" spans="1:14" customHeight="1" ht="13.5">
       <c r="B45" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F45" s="32" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H45" s="33"/>
       <c r="I45" s="33"/>
@@ -1540,10 +1537,10 @@
     </row>
     <row r="47" spans="1:14" customHeight="1" ht="13.5">
       <c r="B47" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F47" s="32" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H47" s="33"/>
       <c r="I47" s="33"/>
@@ -1558,10 +1555,10 @@
     </row>
     <row r="49" spans="1:14" customHeight="1" ht="13.5">
       <c r="B49" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F49" s="32" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H49" s="33"/>
       <c r="I49" s="33"/>
@@ -1576,10 +1573,10 @@
     </row>
     <row r="51" spans="1:14" customHeight="1" ht="13.5">
       <c r="B51" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F51" s="32" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H51" s="33"/>
       <c r="I51" s="33"/>
@@ -1628,7 +1625,7 @@
     </row>
     <row r="55" spans="1:14">
       <c r="B55" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F55" s="18"/>
       <c r="H55" s="18"/>
@@ -1637,19 +1634,19 @@
     <row r="56" spans="1:14" customHeight="1" ht="12">
       <c r="B56" s="11"/>
       <c r="F56" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M56" s="14"/>
     </row>
     <row r="57" spans="1:14" customHeight="1" ht="13.5">
       <c r="B57" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H57" s="33"/>
       <c r="I57" s="33"/>
@@ -1665,10 +1662,10 @@
     </row>
     <row r="59" spans="1:14" customHeight="1" ht="13.5">
       <c r="B59" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F59" s="32" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H59" s="33"/>
       <c r="I59" s="33"/>
@@ -1684,10 +1681,10 @@
     </row>
     <row r="61" spans="1:14" customHeight="1" ht="13.5">
       <c r="B61" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F61" s="32" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H61" s="33"/>
       <c r="I61" s="33"/>
@@ -1703,10 +1700,10 @@
     </row>
     <row r="63" spans="1:14" customHeight="1" ht="13.5">
       <c r="B63" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F63" s="32" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H63" s="33"/>
       <c r="I63" s="33"/>
@@ -1722,10 +1719,10 @@
     </row>
     <row r="65" spans="1:14" customHeight="1" ht="13.5">
       <c r="B65" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H65" s="33"/>
       <c r="I65" s="33"/>
@@ -1741,10 +1738,10 @@
     </row>
     <row r="67" spans="1:14" customHeight="1" ht="13.5">
       <c r="B67" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H67" s="33"/>
       <c r="I67" s="33"/>
@@ -1759,7 +1756,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="B69" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F69" s="33"/>
       <c r="H69" s="33"/>
@@ -1801,19 +1798,19 @@
     <row r="73" spans="1:14">
       <c r="A73" s="18"/>
       <c r="B73" s="56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C73" s="57"/>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
       <c r="F73" s="57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G73" s="57"/>
       <c r="H73" s="57"/>
       <c r="I73" s="57"/>
       <c r="L73" s="57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M73" s="58"/>
     </row>
@@ -1850,7 +1847,7 @@
       <c r="H76" s="49"/>
       <c r="I76" s="49"/>
       <c r="L76" s="49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M76" s="50"/>
     </row>

--- a/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
+++ b/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
@@ -28,13 +28,13 @@
     <t>Fecha de realización:</t>
   </si>
   <si>
-    <t>12/03/2025</t>
+    <t>23/04/2025</t>
   </si>
   <si>
     <t>No. de reporte:</t>
   </si>
   <si>
-    <t>PM12032025</t>
+    <t>PM23042025</t>
   </si>
   <si>
     <t>Programado</t>
@@ -61,25 +61,25 @@
     <t>Puesto:</t>
   </si>
   <si>
-    <t>Tt</t>
+    <t>Soporte 1</t>
   </si>
   <si>
     <t>No. de serie:</t>
   </si>
   <si>
-    <t>TT</t>
-  </si>
-  <si>
     <t>Capacidad de disco:</t>
   </si>
   <si>
-    <t>1GB</t>
+    <t>480GB</t>
   </si>
   <si>
     <t>No. de inventario:</t>
   </si>
   <si>
     <t>Capacidad de memoria:</t>
+  </si>
+  <si>
+    <t>8GB</t>
   </si>
   <si>
     <t>Espacio disponible:</t>
@@ -1147,8 +1147,8 @@
         <v>15</v>
       </c>
       <c r="I17" s="47"/>
-      <c r="J17" s="54" t="s">
-        <v>16</v>
+      <c r="J17" s="54">
+        <v>123455</v>
       </c>
       <c r="K17" s="54"/>
       <c r="L17" s="54"/>
@@ -1161,16 +1161,16 @@
     <row r="19" spans="1:14">
       <c r="A19" s="9"/>
       <c r="B19" s="46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="47"/>
       <c r="D19" s="48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" s="48"/>
       <c r="F19" s="48"/>
       <c r="H19" s="47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I19" s="47"/>
       <c r="J19" s="49"/>
@@ -1185,11 +1185,11 @@
     <row r="21" spans="1:14">
       <c r="A21" s="9"/>
       <c r="B21" s="46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" s="47"/>
       <c r="D21" s="48" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E21" s="48"/>
       <c r="F21" s="48"/>

--- a/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
+++ b/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="58">
   <si>
     <t>Automóviles y Camiones Rivera, S.A. de C.V.</t>
   </si>
@@ -28,13 +28,13 @@
     <t>Fecha de realización:</t>
   </si>
   <si>
-    <t>23/04/2025</t>
+    <t>24/04/2025</t>
   </si>
   <si>
     <t>No. de reporte:</t>
   </si>
   <si>
-    <t>PM23042025</t>
+    <t>PM24042025</t>
   </si>
   <si>
     <t>Programado</t>
@@ -67,6 +67,9 @@
     <t>No. de serie:</t>
   </si>
   <si>
+    <t>ERFGHHKIY</t>
+  </si>
+  <si>
     <t>Capacidad de disco:</t>
   </si>
   <si>
@@ -79,7 +82,7 @@
     <t>Capacidad de memoria:</t>
   </si>
   <si>
-    <t>8GB</t>
+    <t>16GB</t>
   </si>
   <si>
     <t>Espacio disponible:</t>
@@ -170,6 +173,9 @@
   </si>
   <si>
     <t>Exploradores</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Otros</t>
@@ -506,6 +512,33 @@
     </xf>
     <xf xfId="0" fontId="1" numFmtId="14" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -515,17 +548,11 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -536,31 +563,10 @@
     <xf xfId="0" fontId="1" numFmtId="49" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -988,25 +994,25 @@
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
       <c r="F7" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="52" t="s">
+      <c r="H7" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="48" t="s">
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="M7" s="53"/>
+      <c r="M7" s="60"/>
     </row>
     <row r="8" spans="1:14" customHeight="1" ht="7.5">
       <c r="B8" s="11"/>
@@ -1014,19 +1020,19 @@
     </row>
     <row r="9" spans="1:14" customHeight="1" ht="13.5">
       <c r="A9" s="9"/>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="52"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="45" t="s">
         <v>7</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="52" t="s">
+      <c r="H9" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="52"/>
+      <c r="I9" s="51"/>
       <c r="J9" s="45"/>
       <c r="K9" s="13"/>
       <c r="L9" s="9"/>
@@ -1049,22 +1055,22 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="9"/>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="52"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="48" t="s">
+      <c r="E11" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="53"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="60"/>
     </row>
     <row r="12" spans="1:14" customHeight="1" ht="7.5">
       <c r="A12" s="9"/>
@@ -1112,22 +1118,22 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="9"/>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="47"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="21"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="48" t="s">
+      <c r="F15" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="53"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="60"/>
     </row>
     <row r="16" spans="1:14" customHeight="1" ht="7.5">
       <c r="B16" s="11"/>
@@ -1137,22 +1143,22 @@
       <c r="B17" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="H17" s="47" t="s">
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="H17" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="47"/>
-      <c r="J17" s="54">
-        <v>123455</v>
-      </c>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="55"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="62"/>
     </row>
     <row r="18" spans="1:14" customHeight="1" ht="7.5">
       <c r="B18" s="11"/>
@@ -1160,23 +1166,23 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="9"/>
-      <c r="B19" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="48" t="s">
+      <c r="B19" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="H19" s="47" t="s">
+      <c r="C19" s="56"/>
+      <c r="D19" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="I19" s="47"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="50"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="H19" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="56"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="49"/>
     </row>
     <row r="20" spans="1:14" customHeight="1" ht="7.5">
       <c r="B20" s="11"/>
@@ -1184,23 +1190,23 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="9"/>
-      <c r="B21" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="48" t="s">
+      <c r="B21" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
       <c r="H21" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I21" s="21"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="50"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="49"/>
     </row>
     <row r="22" spans="1:14" customHeight="1" ht="7.5">
       <c r="B22" s="11"/>
@@ -1208,22 +1214,22 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="9"/>
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="52"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="50"/>
+      <c r="E23" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="49"/>
     </row>
     <row r="24" spans="1:14" customHeight="1" ht="7.5">
       <c r="A24" s="9"/>
@@ -1263,21 +1269,21 @@
       <c r="M26" s="7"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="B27" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="H27" s="57" t="s">
+      <c r="B27" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="58"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="H27" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="47"/>
     </row>
     <row r="28" spans="1:14" customHeight="1" ht="7.5">
       <c r="A28" s="9"/>
@@ -1289,26 +1295,26 @@
     </row>
     <row r="29" spans="1:14" customHeight="1" ht="13.5">
       <c r="A29" s="9"/>
-      <c r="B29" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="52"/>
+      <c r="B29" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="51"/>
       <c r="D29" s="9"/>
       <c r="E29" s="13" t="s">
         <v>7</v>
       </c>
       <c r="F29" s="9"/>
-      <c r="G29" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="52"/>
-      <c r="I29" s="52"/>
+      <c r="G29" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
       <c r="J29" s="9"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="M29" s="59"/>
+      <c r="M29" s="58"/>
     </row>
     <row r="30" spans="1:14" customHeight="1" ht="7.5">
       <c r="B30" s="28"/>
@@ -1319,30 +1325,30 @@
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
-      <c r="M30" s="60"/>
+      <c r="M30" s="59"/>
     </row>
     <row r="31" spans="1:14" customHeight="1" ht="13.5">
       <c r="A31" s="9"/>
-      <c r="B31" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="52"/>
+      <c r="B31" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="51"/>
       <c r="D31" s="9"/>
       <c r="E31" s="13" t="s">
         <v>7</v>
       </c>
       <c r="F31" s="9"/>
-      <c r="G31" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
+      <c r="G31" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
       <c r="J31" s="9"/>
       <c r="K31" s="13"/>
       <c r="L31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="M31" s="60"/>
+      <c r="M31" s="59"/>
     </row>
     <row r="32" spans="1:14" customHeight="1" ht="7.5">
       <c r="B32" s="8"/>
@@ -1357,20 +1363,20 @@
     </row>
     <row r="33" spans="1:14" customHeight="1" ht="13.5">
       <c r="A33" s="9"/>
-      <c r="B33" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="52"/>
+      <c r="B33" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="51"/>
       <c r="D33" s="9"/>
       <c r="E33" s="13" t="s">
         <v>7</v>
       </c>
       <c r="F33" s="9"/>
-      <c r="G33" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
+      <c r="G33" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
       <c r="J33" s="9"/>
       <c r="K33" s="29"/>
       <c r="L33" s="9"/>
@@ -1389,19 +1395,19 @@
     </row>
     <row r="35" spans="1:14" customHeight="1" ht="13.5">
       <c r="A35" s="9"/>
-      <c r="B35" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="52"/>
+      <c r="B35" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="51"/>
       <c r="D35" s="9"/>
       <c r="E35" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
+      <c r="G35" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
       <c r="J35" s="9"/>
       <c r="K35" s="29"/>
       <c r="L35" s="9"/>
@@ -1420,20 +1426,20 @@
     </row>
     <row r="37" spans="1:14" customHeight="1" ht="13.5">
       <c r="A37" s="9"/>
-      <c r="B37" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="52"/>
+      <c r="B37" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="51"/>
       <c r="D37" s="9"/>
       <c r="E37" s="13" t="s">
         <v>7</v>
       </c>
       <c r="F37" s="18"/>
-      <c r="G37" s="52" t="s">
-        <v>34</v>
-      </c>
-      <c r="H37" s="52"/>
-      <c r="I37" s="52"/>
+      <c r="G37" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
       <c r="J37" s="9"/>
       <c r="K37" s="29"/>
       <c r="L37" s="18"/>
@@ -1485,23 +1491,23 @@
     </row>
     <row r="41" spans="1:14">
       <c r="B41" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M41" s="12"/>
     </row>
     <row r="42" spans="1:14">
       <c r="B42" s="11"/>
       <c r="F42" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M42" s="14"/>
     </row>
     <row r="43" spans="1:14" customHeight="1" ht="13.5">
       <c r="B43" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F43" s="32" t="s">
         <v>7</v>
@@ -1519,7 +1525,7 @@
     </row>
     <row r="45" spans="1:14" customHeight="1" ht="13.5">
       <c r="B45" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F45" s="32" t="s">
         <v>7</v>
@@ -1537,7 +1543,7 @@
     </row>
     <row r="47" spans="1:14" customHeight="1" ht="13.5">
       <c r="B47" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F47" s="32" t="s">
         <v>7</v>
@@ -1555,7 +1561,7 @@
     </row>
     <row r="49" spans="1:14" customHeight="1" ht="13.5">
       <c r="B49" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F49" s="32" t="s">
         <v>7</v>
@@ -1573,7 +1579,7 @@
     </row>
     <row r="51" spans="1:14" customHeight="1" ht="13.5">
       <c r="B51" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F51" s="32" t="s">
         <v>7</v>
@@ -1625,7 +1631,7 @@
     </row>
     <row r="55" spans="1:14">
       <c r="B55" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F55" s="18"/>
       <c r="H55" s="18"/>
@@ -1634,16 +1640,16 @@
     <row r="56" spans="1:14" customHeight="1" ht="12">
       <c r="B56" s="11"/>
       <c r="F56" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M56" s="14"/>
     </row>
     <row r="57" spans="1:14" customHeight="1" ht="13.5">
       <c r="B57" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F57" s="32" t="s">
         <v>7</v>
@@ -1662,7 +1668,7 @@
     </row>
     <row r="59" spans="1:14" customHeight="1" ht="13.5">
       <c r="B59" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F59" s="32" t="s">
         <v>7</v>
@@ -1681,7 +1687,7 @@
     </row>
     <row r="61" spans="1:14" customHeight="1" ht="13.5">
       <c r="B61" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F61" s="32" t="s">
         <v>7</v>
@@ -1700,7 +1706,7 @@
     </row>
     <row r="63" spans="1:14" customHeight="1" ht="13.5">
       <c r="B63" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F63" s="32" t="s">
         <v>7</v>
@@ -1719,7 +1725,7 @@
     </row>
     <row r="65" spans="1:14" customHeight="1" ht="13.5">
       <c r="B65" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F65" s="32" t="s">
         <v>7</v>
@@ -1738,10 +1744,10 @@
     </row>
     <row r="67" spans="1:14" customHeight="1" ht="13.5">
       <c r="B67" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="H67" s="33"/>
       <c r="I67" s="33"/>
@@ -1756,7 +1762,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="B69" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F69" s="33"/>
       <c r="H69" s="33"/>
@@ -1797,27 +1803,27 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="18"/>
-      <c r="B73" s="56" t="s">
-        <v>52</v>
-      </c>
-      <c r="C73" s="57"/>
+      <c r="B73" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="C73" s="46"/>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
-      <c r="F73" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="G73" s="57"/>
-      <c r="H73" s="57"/>
-      <c r="I73" s="57"/>
-      <c r="L73" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="M73" s="58"/>
+      <c r="F73" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="G73" s="46"/>
+      <c r="H73" s="46"/>
+      <c r="I73" s="46"/>
+      <c r="L73" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="M73" s="47"/>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="18"/>
-      <c r="B74" s="63"/>
-      <c r="C74" s="64"/>
+      <c r="B74" s="53"/>
+      <c r="C74" s="54"/>
       <c r="D74" s="18"/>
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
@@ -1834,22 +1840,22 @@
     </row>
     <row r="76" spans="1:14" customHeight="1" ht="33">
       <c r="A76" s="18"/>
-      <c r="B76" s="61" t="s">
+      <c r="B76" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="C76" s="62"/>
+      <c r="C76" s="64"/>
       <c r="D76" s="18"/>
       <c r="E76" s="18"/>
-      <c r="F76" s="49" t="s">
+      <c r="F76" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49"/>
-      <c r="L76" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="M76" s="50"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
+      <c r="L76" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="M76" s="49"/>
     </row>
     <row r="77" spans="1:14" customHeight="1" ht="8.25">
       <c r="B77" s="34"/>
@@ -1871,31 +1877,6 @@
     <row r="79" spans="1:14" customHeight="1" ht="15.75" hidden="true"/>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="L73:M73"/>
-    <mergeCell ref="F76:I76"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="F73:I73"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="M29:M31"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="G31:I31"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="H19:I19"/>
@@ -1912,6 +1893,31 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="J17:M17"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="M29:M31"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="L73:M73"/>
+    <mergeCell ref="F76:I76"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="F73:I73"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B74:C74"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.19685039370079" right="0.19685039370079" top="0" bottom="0" header="0" footer="0.19685039370079"/>

--- a/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
+++ b/imagenes_guardadas/archivo_modificado_mantenimiento.xlsx
@@ -28,13 +28,13 @@
     <t>Fecha de realización:</t>
   </si>
   <si>
-    <t>24/04/2025</t>
+    <t>17/12/2025</t>
   </si>
   <si>
     <t>No. de reporte:</t>
   </si>
   <si>
-    <t>PM24042025</t>
+    <t>PM17122025</t>
   </si>
   <si>
     <t>Programado</t>
@@ -55,25 +55,25 @@
     <t>Nombre del usuario:</t>
   </si>
   <si>
-    <t>Jose Arturo Moreno Aguilar</t>
+    <t>Prueba Jose Prueba Jose Prueba Jose</t>
   </si>
   <si>
     <t>Puesto:</t>
   </si>
   <si>
-    <t>Soporte 1</t>
+    <t>Prueba Jose</t>
   </si>
   <si>
     <t>No. de serie:</t>
   </si>
   <si>
-    <t>ERFGHHKIY</t>
+    <t>PRUEBA JOSE</t>
   </si>
   <si>
     <t>Capacidad de disco:</t>
   </si>
   <si>
-    <t>480GB</t>
+    <t>1GB</t>
   </si>
   <si>
     <t>No. de inventario:</t>
@@ -82,9 +82,6 @@
     <t>Capacidad de memoria:</t>
   </si>
   <si>
-    <t>16GB</t>
-  </si>
-  <si>
     <t>Espacio disponible:</t>
   </si>
   <si>
@@ -100,6 +97,9 @@
     <t>Pantalla</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>Eliminación de cookies</t>
   </si>
   <si>
@@ -175,9 +175,6 @@
     <t>Exploradores</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Otros</t>
   </si>
   <si>
@@ -188,6 +185,9 @@
   </si>
   <si>
     <t>Supervisó</t>
+  </si>
+  <si>
+    <t>José Arturo Moreno Aguilar</t>
   </si>
   <si>
     <t>Abel de Jesús Moral Flores</t>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C21" s="56"/>
       <c r="D21" s="57" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E21" s="57"/>
       <c r="F21" s="57"/>
       <c r="H21" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I21" s="21"/>
       <c r="J21" s="48"/>
@@ -1220,7 +1220,7 @@
       <c r="C23" s="51"/>
       <c r="D23" s="9"/>
       <c r="E23" s="48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F23" s="48"/>
       <c r="G23" s="48"/>
@@ -1270,14 +1270,14 @@
     </row>
     <row r="27" spans="1:14">
       <c r="B27" s="52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="46"/>
       <c r="D27" s="46"/>
       <c r="E27" s="46"/>
       <c r="F27" s="46"/>
       <c r="H27" s="46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I27" s="46"/>
       <c r="J27" s="46"/>
@@ -1296,12 +1296,12 @@
     <row r="29" spans="1:14" customHeight="1" ht="13.5">
       <c r="A29" s="9"/>
       <c r="B29" s="50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="51"/>
       <c r="D29" s="9"/>
       <c r="E29" s="13" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="51" t="s">
@@ -1312,7 +1312,7 @@
       <c r="J29" s="9"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="M29" s="58"/>
     </row>
@@ -1335,7 +1335,7 @@
       <c r="C31" s="51"/>
       <c r="D31" s="9"/>
       <c r="E31" s="13" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="51" t="s">
@@ -1346,7 +1346,7 @@
       <c r="J31" s="9"/>
       <c r="K31" s="13"/>
       <c r="L31" s="13" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="M31" s="59"/>
     </row>
@@ -1369,7 +1369,7 @@
       <c r="C33" s="51"/>
       <c r="D33" s="9"/>
       <c r="E33" s="13" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="51" t="s">
@@ -1401,7 +1401,7 @@
       <c r="C35" s="51"/>
       <c r="D35" s="9"/>
       <c r="E35" s="13" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G35" s="51" t="s">
         <v>33</v>
@@ -1432,7 +1432,7 @@
       <c r="C37" s="51"/>
       <c r="D37" s="9"/>
       <c r="E37" s="13" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F37" s="18"/>
       <c r="G37" s="51" t="s">
@@ -1510,7 +1510,7 @@
         <v>39</v>
       </c>
       <c r="F43" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H43" s="33"/>
       <c r="I43" s="33"/>
@@ -1528,7 +1528,7 @@
         <v>40</v>
       </c>
       <c r="F45" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H45" s="33"/>
       <c r="I45" s="33"/>
@@ -1546,7 +1546,7 @@
         <v>41</v>
       </c>
       <c r="F47" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H47" s="33"/>
       <c r="I47" s="33"/>
@@ -1564,7 +1564,7 @@
         <v>42</v>
       </c>
       <c r="F49" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H49" s="33"/>
       <c r="I49" s="33"/>
@@ -1582,7 +1582,7 @@
         <v>43</v>
       </c>
       <c r="F51" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H51" s="33"/>
       <c r="I51" s="33"/>
@@ -1652,7 +1652,7 @@
         <v>46</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H57" s="33"/>
       <c r="I57" s="33"/>
@@ -1671,7 +1671,7 @@
         <v>47</v>
       </c>
       <c r="F59" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H59" s="33"/>
       <c r="I59" s="33"/>
@@ -1690,7 +1690,7 @@
         <v>48</v>
       </c>
       <c r="F61" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H61" s="33"/>
       <c r="I61" s="33"/>
@@ -1709,7 +1709,7 @@
         <v>49</v>
       </c>
       <c r="F63" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H63" s="33"/>
       <c r="I63" s="33"/>
@@ -1728,7 +1728,7 @@
         <v>50</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H65" s="33"/>
       <c r="I65" s="33"/>
@@ -1747,7 +1747,7 @@
         <v>51</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="H67" s="33"/>
       <c r="I67" s="33"/>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="B69" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F69" s="33"/>
       <c r="H69" s="33"/>
@@ -1804,19 +1804,19 @@
     <row r="73" spans="1:14">
       <c r="A73" s="18"/>
       <c r="B73" s="52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C73" s="46"/>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
       <c r="F73" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G73" s="46"/>
       <c r="H73" s="46"/>
       <c r="I73" s="46"/>
       <c r="L73" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M73" s="47"/>
     </row>
@@ -1847,7 +1847,7 @@
       <c r="D76" s="18"/>
       <c r="E76" s="18"/>
       <c r="F76" s="48" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="G76" s="48"/>
       <c r="H76" s="48"/>
